--- a/data-raw/rap_2026/Luku3.xlsx
+++ b/data-raw/rap_2026/Luku3.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Tuottavuuslautakunta\Raportti_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\03238715\Work Folders\R_pkg\fiprod\data-raw\rap_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75EAA6F-6B69-45E6-809F-80CBBB71C5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FA2366-C9C5-40A1-B971-FA29703D9CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38480" yWindow="-80" windowWidth="38560" windowHeight="21040" activeTab="3" xr2:uid="{96E585B6-5D10-42B8-AFD4-413E8DBD53EE}"/>
+    <workbookView xWindow="4776" yWindow="1344" windowWidth="17280" windowHeight="10572" activeTab="4" xr2:uid="{96E585B6-5D10-42B8-AFD4-413E8DBD53EE}"/>
   </bookViews>
   <sheets>
     <sheet name="kuvio1" sheetId="2" r:id="rId1"/>
     <sheet name="kuvio2" sheetId="1" r:id="rId2"/>
     <sheet name="kuvio3" sheetId="4" r:id="rId3"/>
     <sheet name="kuvio4" sheetId="3" r:id="rId4"/>
+    <sheet name="Kuvio11" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="139">
   <si>
     <t>geo</t>
   </si>
@@ -238,20 +239,263 @@
   <si>
     <t>Moottoriajoneuvojen huolto ja korjaus (G45201)</t>
   </si>
+  <si>
+    <t>(S951).</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>communication</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>computers</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>Repair</t>
+  </si>
+  <si>
+    <t>(N77–82);</t>
+  </si>
+  <si>
+    <t>activities</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>75);</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>(excluding</t>
+  </si>
+  <si>
+    <t>(M69–74)</t>
+  </si>
+  <si>
+    <t>technical</t>
+  </si>
+  <si>
+    <t>scientific,</t>
+  </si>
+  <si>
+    <t>Professional,</t>
+  </si>
+  <si>
+    <t>(L68);</t>
+  </si>
+  <si>
+    <t>estate</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>(J58–63);</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>(I55–56);</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>Accommodation</t>
+  </si>
+  <si>
+    <t>(H49–53);</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>(G45–47);</t>
+  </si>
+  <si>
+    <t>motorcycles</t>
+  </si>
+  <si>
+    <t>vehicles</t>
+  </si>
+  <si>
+    <t>motor</t>
+  </si>
+  <si>
+    <t>repair</t>
+  </si>
+  <si>
+    <t>trade;</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>Wholesale</t>
+  </si>
+  <si>
+    <t>are:</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>listed</t>
+  </si>
+  <si>
+    <t>industries</t>
+  </si>
+  <si>
+    <t>Rev.</t>
+  </si>
+  <si>
+    <t>NACE</t>
+  </si>
+  <si>
+    <t>The</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Very high</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Very low</t>
+  </si>
+  <si>
+    <t>Support Serv</t>
+  </si>
+  <si>
+    <t>Prof. Activ.</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Inform. &amp; Comm.</t>
+  </si>
+  <si>
+    <t>Accom. &amp; Rest</t>
+  </si>
+  <si>
+    <t>Logistic</t>
+  </si>
+  <si>
+    <t>Erittäin korkea</t>
+  </si>
+  <si>
+    <t>Korkea</t>
+  </si>
+  <si>
+    <t>Matala</t>
+  </si>
+  <si>
+    <t>Erittäin matala</t>
+  </si>
+  <si>
+    <t>Tukipalvelut</t>
+  </si>
+  <si>
+    <t>Asiantuntijapalvelut</t>
+  </si>
+  <si>
+    <t>Kiinteistöala</t>
+  </si>
+  <si>
+    <t>Informaatio ja viestintä</t>
+  </si>
+  <si>
+    <t>Majoitus- ja ravitsemistoiminta</t>
+  </si>
+  <si>
+    <t>Kuljetus ja varastointi</t>
+  </si>
+  <si>
+    <t>Kauppa</t>
+  </si>
+  <si>
+    <t>Trade</t>
+  </si>
+  <si>
+    <t>DII</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Kuvio 11. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yritysten jakautuminen digitaalisen intensiteetin luokkiin yksityisil-lä palvelualoilla.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0\ %"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -390,11 +634,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -409,51 +655,59 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+  <cellStyles count="4">
+    <cellStyle name="Normaali" xfId="0" builtinId="0"/>
+    <cellStyle name="Normaali 2" xfId="2" xr:uid="{2F48CCBA-C149-4748-A5B1-FD4789136803}"/>
+    <cellStyle name="Prosenttia" xfId="1" builtinId="5"/>
+    <cellStyle name="Prosenttia 2" xfId="3" xr:uid="{C050CBD0-F1B2-446F-AD7E-1E662F21C7F7}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -471,7 +725,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -944,7 +1198,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1116,9 +1370,9 @@
                     <a:fld id="{CA575526-2884-4952-ABE0-5BBB4FC90205}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1154,9 +1408,9 @@
                     <a:fld id="{17B75EAE-6076-46CD-A9F0-285FF7D0FE66}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1183,12 +1437,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E4DC8B3E-93DA-420C-8BAA-ADDD2B15DC8D}" type="CELLRANGE">
+                    <a:fld id="{0C749D33-8823-4DBF-AF84-041485351A5B}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1216,12 +1470,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7F0FB171-51B5-45C3-8011-55E660B9AC59}" type="CELLRANGE">
+                    <a:fld id="{3EAA424A-FD3E-4C60-8A32-3499AEED3BF3}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1249,12 +1503,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8BC33418-59EB-4E77-96CF-4BA2D5102733}" type="CELLRANGE">
+                    <a:fld id="{A2B75C48-2883-4FB2-911B-62A7CFD63E24}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1282,12 +1536,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1CAD229D-1CAE-41D4-AF51-E51E908F1314}" type="CELLRANGE">
+                    <a:fld id="{63CFD822-B11E-46A7-B377-6CBDE6FFCA28}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1315,12 +1569,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4F251D7C-0D12-41F9-BC54-A45697093BE7}" type="CELLRANGE">
+                    <a:fld id="{6E0E388D-C150-4FF8-B9BE-4515EFE59098}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1357,9 +1611,9 @@
                     <a:fld id="{E91F82F2-CAD9-49D0-A2AF-7986CD815B40}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1386,12 +1640,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{539E576C-4A6F-4411-9B45-9082BBEA1DE6}" type="CELLRANGE">
+                    <a:fld id="{F159F3C0-F49A-4E23-9B45-8AE351C17A61}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1419,12 +1673,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F3C4E250-3467-4B30-B91D-0D3C961E9C0B}" type="CELLRANGE">
+                    <a:fld id="{ED882FA5-A051-4958-8A57-D5B94F9955C1}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1452,12 +1706,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FBC2C858-008C-460D-B56B-85D791A890B5}" type="CELLRANGE">
+                    <a:fld id="{05C35E3B-5C66-4B92-AC29-F3650F16B413}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1485,12 +1739,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{153DC3F4-7412-4007-8B4D-7E4A74AEA2FD}" type="CELLRANGE">
+                    <a:fld id="{2C02B0C1-2FF6-4ABB-9D30-30E2E5B608DA}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1527,9 +1781,9 @@
                     <a:fld id="{5D4A11BC-ED42-4DBA-BB5F-7ADBC35406E2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1556,12 +1810,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5ABE2075-DCFC-43B8-BDD4-AF095DF94591}" type="CELLRANGE">
+                    <a:fld id="{42B1F9F9-3154-44C2-9DF7-0A959A219920}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1589,12 +1843,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D3DCF7E1-3DA2-4835-A568-743333D1216B}" type="CELLRANGE">
+                    <a:fld id="{04E5A2FB-34CC-4B3E-8B87-288EE493460A}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1631,9 +1885,9 @@
                     <a:fld id="{20D01411-D6A7-4087-BF5D-A5894C365BD0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1687,12 +1941,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{49111BA3-D49E-4463-8924-F236D9E3F937}" type="CELLRANGE">
+                    <a:fld id="{E3A60F80-6DCA-4F54-8BDE-7CF7A6D2C595}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1720,12 +1974,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A6D92F46-B650-4F12-9FD8-47D02624B939}" type="CELLRANGE">
+                    <a:fld id="{CE5095CE-8B6C-4B1D-9557-BF196C2DB580}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1753,12 +2007,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5EAA65E-CC32-4863-8EF0-4D24E6ABE5D7}" type="CELLRANGE">
+                    <a:fld id="{DDCC1B0A-BBCB-4B7E-9BF4-D0944B733BC6}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1786,12 +2040,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F9A54AB2-ABCE-4661-9350-9CD3F224E8EA}" type="CELLRANGE">
+                    <a:fld id="{295A1BC3-339F-49F8-B0C7-4BABAEADE956}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1828,9 +2082,9 @@
                     <a:fld id="{B1083348-F1F9-421D-A5E6-1FD02B9D2736}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1866,9 +2120,9 @@
                     <a:fld id="{408711EE-F7D8-4ED2-AAA8-802EF5A3D09D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1904,9 +2158,9 @@
                     <a:fld id="{509BE717-E778-40AA-AC6F-0C6271E93274}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1942,9 +2196,9 @@
                     <a:fld id="{25853CFC-32BB-44D1-ACF6-7B3FA5A7DE11}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1971,12 +2225,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A28ECDAC-B194-4A27-B422-FD464C4167FD}" type="CELLRANGE">
+                    <a:fld id="{F6279AC5-5316-46AA-8733-D7BD08507949}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2004,12 +2258,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{36CAD97C-B894-418F-B55C-BA77197ED8E4}" type="CELLRANGE">
+                    <a:fld id="{842C4AA9-E5B8-43B7-A23A-010AA3CE0BFB}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2702,7 +2956,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2874,9 +3128,9 @@
                     <a:fld id="{58F54F44-BC92-4F1E-AFC4-512E301B686A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2912,9 +3166,9 @@
                     <a:fld id="{7B850FCA-5816-4EDB-9F83-562823493621}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2941,12 +3195,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{435FC3EE-3311-4339-8ED7-3626C118C5DD}" type="CELLRANGE">
+                    <a:fld id="{D815416C-BE18-4C59-AB93-B6ACFE59CCAF}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -2974,12 +3228,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{01552E6D-5D32-487C-8051-69367582CC6F}" type="CELLRANGE">
+                    <a:fld id="{E6DB33E9-0BC8-4849-897A-96C84A787C38}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3007,12 +3261,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DACAD5DA-325F-4B23-B088-FCEE18B59FEC}" type="CELLRANGE">
+                    <a:fld id="{602219CE-9E79-4F57-9350-ADFDE4A5F7D9}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3040,12 +3294,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5B0046D7-60B3-44F3-8F33-78A5F2FEF4B9}" type="CELLRANGE">
+                    <a:fld id="{BC005808-C24A-4D6F-A61C-66DE1E4D775C}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3073,12 +3327,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7AA693E1-2900-4A9E-9603-09AB91BDBA21}" type="CELLRANGE">
+                    <a:fld id="{46F1EDA4-4979-4C4A-9459-D66B8CFA03B4}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3106,12 +3360,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9E06ED78-1382-4638-8210-6F212C73CC26}" type="CELLRANGE">
+                    <a:fld id="{4A2C9BB5-26B6-4778-B4BF-DA75C07F83F4}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3139,12 +3393,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A6F340A2-B5D2-44CB-8E23-630E969D54B4}" type="CELLRANGE">
+                    <a:fld id="{95892A6A-B195-4A94-AF3D-2BA677110C4E}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3181,9 +3435,9 @@
                     <a:fld id="{FF24ADD6-43E7-4486-AFAE-2E304DB33082}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3219,9 +3473,9 @@
                     <a:fld id="{199CE5B1-9CF1-499D-842C-8CD191919C73}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3248,12 +3502,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8D1D652E-7A76-4C0E-A623-0A8A93143FE0}" type="CELLRANGE">
+                    <a:fld id="{31A18128-A45E-4B50-A3E2-0F0A73D973D7}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3281,12 +3535,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CECE7878-78A0-43BB-A340-A5229ACDC427}" type="CELLRANGE">
+                    <a:fld id="{2D035888-A6BC-4E0A-8C9A-3C00A636035C}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3323,9 +3577,9 @@
                     <a:fld id="{8BC02C83-2372-4D15-B52C-43B1BE5B776B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3352,12 +3606,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5C59EC2-EF91-456F-AA2C-85901C576EFD}" type="CELLRANGE">
+                    <a:fld id="{0E09C275-2C1F-4EB8-846A-D2E9D96FB970}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3394,9 +3648,9 @@
                     <a:fld id="{87A93685-7630-450B-818A-E21E481056E1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3450,12 +3704,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9F7DC500-37F8-4697-AC68-C829302730F8}" type="CELLRANGE">
+                    <a:fld id="{630EE788-9B74-402D-ADC8-82428BDFA58D}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3483,12 +3737,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{46599302-CE64-45C3-B5ED-00FF6A8E1CF7}" type="CELLRANGE">
+                    <a:fld id="{C9F39B30-B8A7-402C-A56B-D83A226C2B11}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3516,12 +3770,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25C001DC-04BE-430E-9BFB-E26864069BEF}" type="CELLRANGE">
+                    <a:fld id="{F499ED54-B478-459E-9B3F-83055DA01C6B}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3549,12 +3803,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{94D832D7-0F56-4E78-B718-7DC3A64D6BB5}" type="CELLRANGE">
+                    <a:fld id="{22276ED4-29FE-4F89-B6F3-0BF8B7415EBE}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3591,9 +3845,9 @@
                     <a:fld id="{4A152926-99FB-40B8-9E24-D4BC0FF6547B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3620,12 +3874,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C06487E1-C436-46FD-8F9D-DB0CA967EE4F}" type="CELLRANGE">
+                    <a:fld id="{8508AF06-E221-4CE2-8C3E-471C7801011A}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3662,9 +3916,9 @@
                     <a:fld id="{A714B15A-8CE0-490D-8344-655AF75EFECC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3700,9 +3954,9 @@
                     <a:fld id="{F99269AF-5E97-43B6-A136-0FA7A92FC221}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3738,9 +3992,9 @@
                     <a:fld id="{E37F49B5-8D47-4CB6-9663-943448B44E51}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3767,12 +4021,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D53BB8EA-F830-45C1-95E2-03926FED4710}" type="CELLRANGE">
+                    <a:fld id="{65C175D9-F250-4E88-A837-E19D18109132}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4465,7 +4719,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4637,9 +4891,9 @@
                     <a:fld id="{FC2E6ED4-85C2-4F6F-98BD-723AFB0D5E04}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4675,9 +4929,9 @@
                     <a:fld id="{E57FDD00-3600-4B4C-AB92-F6966CB69E6B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4713,9 +4967,9 @@
                     <a:fld id="{EDC80406-5BD0-4CF9-8460-C4DCB5DCBA20}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4751,9 +5005,9 @@
                     <a:fld id="{F800F37F-9E12-40A8-B874-B01A5CD0EDC3}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4789,9 +5043,9 @@
                     <a:fld id="{2316417B-68A0-4B7D-9272-8173F9ABE559}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4818,12 +5072,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{76972F00-8C50-499B-9304-D4F151216C12}" type="CELLRANGE">
+                    <a:fld id="{36DC4B33-6763-4E9A-8982-33487A36AFBC}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4860,9 +5114,9 @@
                     <a:fld id="{1E45FB5E-CB51-4581-B801-543FB41A13FF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4889,12 +5143,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{18044A04-1DD6-4637-9B4F-6C1118BCE335}" type="CELLRANGE">
+                    <a:fld id="{13B6844D-7A86-4B3A-9251-7124A19E14A1}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4922,12 +5176,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0733B16E-3592-48DF-8C34-D0AF8D950E08}" type="CELLRANGE">
+                    <a:fld id="{8759FCBF-EBE4-44FD-AE24-71CA83E48F5E}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -4964,9 +5218,9 @@
                     <a:fld id="{6BDB9B2D-4DC4-490A-B3EA-F4118B483502}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5002,9 +5256,9 @@
                     <a:fld id="{C32FA206-3BE8-4600-B804-FB7B92BD3F08}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5031,12 +5285,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51DE6EEA-A942-4F76-88A3-A104D4CFE6A9}" type="CELLRANGE">
+                    <a:fld id="{6327E36D-713F-4255-881D-6F410D9AF838}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5064,12 +5318,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{22A7C8F5-6396-4505-93E4-5950FC03717A}" type="CELLRANGE">
+                    <a:fld id="{CEB6C4D0-0252-4886-93F7-6DEE4BC52E39}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5124,12 +5378,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AE2BEC8D-DF43-4009-A322-603DE30EAFB6}" type="CELLRANGE">
+                    <a:fld id="{D1A4F35A-2483-45D4-B20D-DF00F520AD59}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5166,9 +5420,9 @@
                     <a:fld id="{0807B72D-62EC-4375-882D-D336B9A27FE5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5231,9 +5485,9 @@
                     <a:fld id="{60DE113C-0647-457A-B747-E8B56C386305}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5269,9 +5523,9 @@
                     <a:fld id="{51B424F9-F67F-4FE1-8BEB-CDBEB54876C6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5307,9 +5561,9 @@
                     <a:fld id="{42CC4C6E-259B-4373-8C9D-8B9C1C4E1345}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5336,12 +5590,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{06085D05-9100-4AE8-8AA2-F5974AAA77AC}" type="CELLRANGE">
+                    <a:fld id="{FBC302E7-9DD2-47A4-A9D9-16FC72D5462D}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5378,9 +5632,9 @@
                     <a:fld id="{C7B35DFB-16AD-47FF-8329-1FB0A00D20BF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5407,12 +5661,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3AE8C14C-0341-44DB-81FF-BC42B2180D28}" type="CELLRANGE">
+                    <a:fld id="{32AA6E53-0E08-49A9-9D48-F36DD0616184}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5440,12 +5694,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{599C1EF6-9292-479A-A28E-8AF235BB47A2}" type="CELLRANGE">
+                    <a:fld id="{5F5EF077-5AE7-4588-8CC9-E8265FD0BD8F}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5473,12 +5727,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A686F477-BD5B-4E3A-A128-1B6021ABFF18}" type="CELLRANGE">
+                    <a:fld id="{C6150EAE-163C-4062-8DFB-C6CDC312F624}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5506,12 +5760,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6CAAF5AF-F611-4B1D-82CD-DE3342267FAD}" type="CELLRANGE">
+                    <a:fld id="{E9696D30-6D4C-45C4-AE5D-30AFE65E8C9B}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -5539,12 +5793,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{01B8E1E5-FE94-4EE5-86A3-1AB981F22B63}" type="CELLRANGE">
+                    <a:fld id="{91B7AFA6-3189-46D5-9164-C5495B8BB341}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6230,7 +6484,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6408,9 +6662,9 @@
                     <a:fld id="{CDEEA5FE-03CA-44BA-9416-415E16AA76EC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6446,9 +6700,9 @@
                     <a:fld id="{116BA446-167E-491B-9677-DAE4E0EB131A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6475,12 +6729,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F451292C-F056-40E4-AC64-7B958678F2CD}" type="CELLRANGE">
+                    <a:fld id="{5DD962F0-D663-43C5-B695-2E1CA5153A1F}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6508,12 +6762,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{91927DDE-054D-4857-A0AC-FFB1136F70EE}" type="CELLRANGE">
+                    <a:fld id="{E5C9E458-81A3-4EDA-9FAA-03A2697D4319}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6541,12 +6795,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4741E1CE-B2AA-4425-B8BD-398250A0B075}" type="CELLRANGE">
+                    <a:fld id="{E475BA08-3D63-485D-8094-A4127984E3E6}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6574,12 +6828,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{47DDDFA2-9415-4DED-BCD9-AD21D5E45ED8}" type="CELLRANGE">
+                    <a:fld id="{56020500-9E42-4D0A-8284-81CE2AC3B012}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6607,12 +6861,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{27AD4752-AC22-4382-BD99-23F9FA2BBF5F}" type="CELLRANGE">
+                    <a:fld id="{666E80D8-5D1B-479B-AE34-361726E67BD8}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6640,12 +6894,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BC8931DB-D3ED-4FA4-8436-2C1C016AB6ED}" type="CELLRANGE">
+                    <a:fld id="{761A173F-1B43-46C2-9A2A-6C2E06810592}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6673,12 +6927,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{488F3CF4-16AF-42CE-AC56-FDBA46284875}" type="CELLRANGE">
+                    <a:fld id="{C93C128B-786D-46A5-A7CC-C99BB885538F}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6706,12 +6960,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{294625C5-1170-4382-9806-E76BE23432B0}" type="CELLRANGE">
+                    <a:fld id="{813D214A-D463-46D5-87BA-D1370C5BB333}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6739,12 +6993,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D5AE438-43BF-450B-AEBE-800095BB04F7}" type="CELLRANGE">
+                    <a:fld id="{9B5E48DE-593E-44EE-B38F-F85CECE2C86D}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6772,12 +7026,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{79D4FF2F-0B26-4C08-9470-66198D7805F3}" type="CELLRANGE">
+                    <a:fld id="{42127FCD-3DB6-49D7-989F-E26B8277FA5B}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6805,12 +7059,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2CC8FC77-E176-4451-BBD8-357899CC1BC7}" type="CELLRANGE">
+                    <a:fld id="{19705CBD-B16C-49B8-A077-E67E172F95EB}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6838,12 +7092,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D7A9813D-0FA2-471C-BBAC-3E146E22195A}" type="CELLRANGE">
+                    <a:fld id="{77B3DAAF-FE46-4518-B62E-D40F94F1A114}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6871,12 +7125,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{94548EBA-6D0E-4F19-9DFE-F42755F4E7C2}" type="CELLRANGE">
+                    <a:fld id="{CB274076-D93E-4234-9BF6-7EDE5C482154}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6904,12 +7158,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{800CD9ED-8595-4929-B28E-D0051AF196E2}" type="CELLRANGE">
+                    <a:fld id="{998BC913-1C08-4855-ABC1-9694D1FD74F4}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6964,12 +7218,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A808C84D-B9E4-4572-B09E-F2593A4A2F17}" type="CELLRANGE">
+                    <a:fld id="{353AD076-C4D2-4553-8B34-7DC2C3526A40}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -6997,12 +7251,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68B9AF6E-8457-4200-88E4-A148CE17004E}" type="CELLRANGE">
+                    <a:fld id="{9E1A1B20-ECE5-4FBF-B63D-B2798E7F3980}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7030,12 +7284,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3D16F8AE-E6AE-4EE1-A429-2766CB60D966}" type="CELLRANGE">
+                    <a:fld id="{838F6268-F0CF-459C-943C-58CA2C0B331A}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7063,12 +7317,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{306B79C0-C657-41A0-8E37-E9AF4CB374FE}" type="CELLRANGE">
+                    <a:fld id="{992E8A3B-6CA2-4DED-AD8A-7E436EAEC6A3}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7096,12 +7350,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{29F348A4-5928-4257-A445-E1B9F7A4E154}" type="CELLRANGE">
+                    <a:fld id="{5AC4ADCD-4CD6-41ED-8CD6-FA95E8340C03}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7129,12 +7383,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A8E5721C-A6F5-49AD-ACA5-648D40E2C016}" type="CELLRANGE">
+                    <a:fld id="{B6F92CEB-769D-4311-A111-67CC2170A32B}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7162,12 +7416,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{531A1706-A1F0-4BC6-9C00-0FA4120E88A1}" type="CELLRANGE">
+                    <a:fld id="{D96976A0-F7B1-48BD-AC9D-4069BC3D575E}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7195,12 +7449,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FB96CD45-B418-4376-B7AE-B1FD625E0CBC}" type="CELLRANGE">
+                    <a:fld id="{0CA01CC4-53E9-4131-B884-5D5C11768196}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7228,12 +7482,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F9ECCF46-0C79-4BFB-B03F-CD5869060DC5}" type="CELLRANGE">
+                    <a:fld id="{1B8873EA-D74D-4444-986C-3C5279317475}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7261,12 +7515,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3326544D-6C31-4C3C-AF49-3DEF407E051F}" type="CELLRANGE">
+                    <a:fld id="{CA1FEDF5-2DBA-4399-B76E-9661F17F3972}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -7962,7 +8216,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8142,9 +8396,9 @@
                     <a:fld id="{51EBFC6C-1EC1-43AA-8F44-ED2EB0037101}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8180,9 +8434,9 @@
                     <a:fld id="{AF290517-9DC3-4F3C-B924-A9E447CBB0E8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8209,12 +8463,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37EE392D-BD51-4A0C-B206-9A404A7A53FE}" type="CELLRANGE">
+                    <a:fld id="{A4E97AFF-4C4F-4F89-B8CA-F772B867B334}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8242,12 +8496,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2D0FC710-64FE-4B30-AF25-CBED805CED45}" type="CELLRANGE">
+                    <a:fld id="{40366017-2591-4F4C-9F65-8421953C0C54}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8275,12 +8529,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D7571E5B-4310-4878-BF0E-5A31CA080702}" type="CELLRANGE">
+                    <a:fld id="{A2FBE0E4-D8B1-4CE5-91FF-ADB17A8F9A45}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8308,12 +8562,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{81467880-F703-4399-9503-4BFAC9D7C94A}" type="CELLRANGE">
+                    <a:fld id="{CA7C14FA-E564-4254-9F53-09EF4E5AD180}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8341,12 +8595,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{77A35A14-5757-4040-A850-F14AE71EC7F2}" type="CELLRANGE">
+                    <a:fld id="{5E659B03-3DE4-4087-8923-A9579421ED29}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8374,12 +8628,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5C6BBC29-F8A6-44B6-B386-32FBF7B7BF50}" type="CELLRANGE">
+                    <a:fld id="{38E4608F-1194-4B42-B248-A233318C2B97}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8407,12 +8661,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D2A99DD-503C-48EF-8709-03F2C3452F97}" type="CELLRANGE">
+                    <a:fld id="{2E362CED-E797-491F-8377-53B848767FBD}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8449,9 +8703,9 @@
                     <a:fld id="{13FB6E5B-E12D-4B22-8588-E2F970B02F76}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8478,12 +8732,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25CEB67F-44A7-475B-9A0F-078B8AA4C2A8}" type="CELLRANGE">
+                    <a:fld id="{B044068C-2B88-4A7C-98D4-CBAD6767D159}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8511,12 +8765,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E3CC62FE-F216-422A-9927-3493FBF84BBA}" type="CELLRANGE">
+                    <a:fld id="{4FD45E8A-CA9D-46C2-B201-75254826CC9B}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8544,12 +8798,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EEB0824B-4D69-43CE-A535-B55F7A7E3941}" type="CELLRANGE">
+                    <a:fld id="{9D1CA947-7D09-4A24-92E1-5AB4493F7D78}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8586,9 +8840,9 @@
                     <a:fld id="{3A6A70B1-0F0C-4DFB-B6E8-B455C7D62555}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8615,12 +8869,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9989F4E1-ABE9-4B2A-A740-E5417A99BA09}" type="CELLRANGE">
+                    <a:fld id="{4BFCF0D9-DD53-430E-8647-44A80A589B68}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8648,12 +8902,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8E2D8CD1-5589-431C-8176-555A20018900}" type="CELLRANGE">
+                    <a:fld id="{5A89A886-6B98-4EAB-8FD7-3D1FD99FB05D}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8708,12 +8962,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BAEA3D02-1E29-4126-844A-5B0A01606C26}" type="CELLRANGE">
+                    <a:fld id="{E78CD33D-5A59-4C23-8BC7-CDEAE552D829}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8741,12 +8995,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6BE82DDB-61E6-4779-8BD5-CF5E58DD4DEA}" type="CELLRANGE">
+                    <a:fld id="{3E93D409-6E9D-455E-8F3A-87AED48F6C3E}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8774,12 +9028,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E1B0B78C-BAD7-4ABD-B5BD-31671599B4AC}" type="CELLRANGE">
+                    <a:fld id="{E754701F-C97F-48A6-9C52-09EA4230BFE4}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8807,12 +9061,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B45691EB-9C36-46F6-8E6B-09694F9FB7DF}" type="CELLRANGE">
+                    <a:fld id="{346ACD4C-624E-4B22-8471-8F19A51CD675}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8840,12 +9094,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C682F6E-7183-476E-8520-25B116055577}" type="CELLRANGE">
+                    <a:fld id="{9CCAB598-8AB6-438A-BA64-83073F0C00C8}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8873,12 +9127,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B06DE001-B108-4793-B23A-D9B0AF61CB49}" type="CELLRANGE">
+                    <a:fld id="{5966404D-869C-448B-8CB2-CFAE610CD254}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8906,12 +9160,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BAF1FA5B-312F-4532-9852-4D5F32A72F75}" type="CELLRANGE">
+                    <a:fld id="{B64DEAF0-2C41-4EB0-B3F3-E53C01A1CDFF}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8939,12 +9193,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7939106F-1EB3-42C8-BF64-9F8E4D8CABB3}" type="CELLRANGE">
+                    <a:fld id="{73B42B77-0D9B-43B0-BBF0-416B5AF06F70}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -8972,12 +9226,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5DAE8889-EBB6-42DD-91A9-646C3535C0B1}" type="CELLRANGE">
+                    <a:fld id="{002DEC2F-AFEB-4693-8096-9222A961A2C9}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -9005,12 +9259,12 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E4432753-FFE2-4B64-80BA-CF9B68491780}" type="CELLRANGE">
+                    <a:fld id="{0A5B690E-675D-4A94-86D9-BDF9E6FAAC91}" type="CELLRANGE">
                       <a:rPr lang="fi-FI"/>
                       <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
+                      <a:t>[SOLUALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="LID4096"/>
+                    <a:endParaRPr lang="fi-FI"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -9704,7 +9958,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10011,7 +10265,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fi-FI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10958,6 +11212,1022 @@
           <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fi-FI"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.4006135932227592E-2"/>
+          <c:y val="4.3222003929273084E-2"/>
+          <c:w val="0.87589788501195376"/>
+          <c:h val="0.80239235026708966"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$K$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Kauppa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Kuvio11!$J$5:$J$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Erittäin matala</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Matala</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Korkea</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erittäin korkea</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$K$5:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.35499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42799999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$L$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Kuljetus ja varastointi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Kuvio11!$J$5:$J$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Erittäin matala</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Matala</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Korkea</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erittäin korkea</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$L$5:$L$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.217</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.38299999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$M$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Majoitus- ja ravitsemistoiminta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$M$5:$M$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.17899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.29699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26500000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$N$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Informaatio ja viestintä</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$N$5:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0" formatCode="0.0\ %">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.54299999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.34899999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$O$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Kiinteistöala</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$O$5:$O$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.36299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7000000000000003E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$P$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Asiantuntijapalvelut</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$P$5:$P$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.2000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.22899999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.501</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.248</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Kuvio11!$Q$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tukipalvelut</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Kuvio11!$Q$5:$Q$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.11900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.312</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.439</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.129</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-FE36-42E4-89CE-26FB6C57E4B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="1022795487"/>
+        <c:axId val="1022311551"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1022795487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1022311551"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1022311551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1022795487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.9539829015683173E-2"/>
+          <c:y val="0.91916167664670667"/>
+          <c:w val="0.87080245386434496"/>
+          <c:h val="8.0838323353293412E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -11290,6 +12560,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="231">
   <cs:axisTitle>
@@ -15325,6 +16635,530 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -15654,8 +17488,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F75E8623-7B81-418A-AA21-8E871B40B6C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-teema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -15972,7 +17849,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C420F6-6EF7-4B66-9FF8-9A1A5B197FEF}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -16313,7 +18190,7 @@
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C28" s="12"/>
     </row>
-    <row r="37" spans="6:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F37" s="11" t="s">
         <v>36</v>
       </c>
@@ -16327,9 +18204,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE4514C-6899-480F-AABA-ED7D8D73DC66}">
   <dimension ref="A2:BM112"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:65" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:65" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>35</v>
       </c>
@@ -16386,7 +18263,7 @@
       <c r="AX4" s="2"/>
       <c r="AY4" s="2"/>
     </row>
-    <row r="5" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>2</v>
       </c>
@@ -16412,7 +18289,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:65" ht="25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>0</v>
       </c>
@@ -16492,7 +18369,7 @@
       <c r="AY7" s="4"/>
       <c r="AZ7" s="4"/>
     </row>
-    <row r="8" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>3</v>
       </c>
@@ -16558,7 +18435,7 @@
       <c r="BL8" s="2"/>
       <c r="BM8" s="2"/>
     </row>
-    <row r="9" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
@@ -16624,7 +18501,7 @@
       <c r="BL9" s="2"/>
       <c r="BM9" s="2"/>
     </row>
-    <row r="10" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>32</v>
       </c>
@@ -16690,7 +18567,7 @@
       <c r="BL10" s="2"/>
       <c r="BM10" s="2"/>
     </row>
-    <row r="11" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
@@ -16756,7 +18633,7 @@
       <c r="BL11" s="2"/>
       <c r="BM11" s="2"/>
     </row>
-    <row r="12" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
@@ -16822,7 +18699,7 @@
       <c r="BL12" s="2"/>
       <c r="BM12" s="2"/>
     </row>
-    <row r="13" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
@@ -16888,7 +18765,7 @@
       <c r="BL13" s="2"/>
       <c r="BM13" s="2"/>
     </row>
-    <row r="14" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
@@ -16954,7 +18831,7 @@
       <c r="BL14" s="2"/>
       <c r="BM14" s="2"/>
     </row>
-    <row r="15" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
@@ -17020,7 +18897,7 @@
       <c r="BL15" s="2"/>
       <c r="BM15" s="2"/>
     </row>
-    <row r="16" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
@@ -17086,7 +18963,7 @@
       <c r="BL16" s="2"/>
       <c r="BM16" s="2"/>
     </row>
-    <row r="17" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>15</v>
       </c>
@@ -17152,7 +19029,7 @@
       <c r="BL17" s="2"/>
       <c r="BM17" s="2"/>
     </row>
-    <row r="18" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>16</v>
       </c>
@@ -17218,7 +19095,7 @@
       <c r="BL18" s="2"/>
       <c r="BM18" s="2"/>
     </row>
-    <row r="19" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>33</v>
       </c>
@@ -17284,7 +19161,7 @@
       <c r="BL19" s="2"/>
       <c r="BM19" s="2"/>
     </row>
-    <row r="20" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>17</v>
       </c>
@@ -17350,7 +19227,7 @@
       <c r="BL20" s="2"/>
       <c r="BM20" s="2"/>
     </row>
-    <row r="21" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>18</v>
       </c>
@@ -17412,7 +19289,7 @@
       <c r="BL21" s="2"/>
       <c r="BM21" s="2"/>
     </row>
-    <row r="22" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>19</v>
       </c>
@@ -17478,7 +19355,7 @@
       <c r="BL22" s="2"/>
       <c r="BM22" s="2"/>
     </row>
-    <row r="23" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>20</v>
       </c>
@@ -17544,7 +19421,7 @@
       <c r="BL23" s="2"/>
       <c r="BM23" s="2"/>
     </row>
-    <row r="24" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>21</v>
       </c>
@@ -17590,7 +19467,7 @@
       <c r="BL24" s="2"/>
       <c r="BM24" s="2"/>
     </row>
-    <row r="25" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>22</v>
       </c>
@@ -17657,7 +19534,7 @@
       <c r="BL25" s="2"/>
       <c r="BM25" s="2"/>
     </row>
-    <row r="26" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>23</v>
       </c>
@@ -17723,7 +19600,7 @@
       <c r="BL26" s="2"/>
       <c r="BM26" s="2"/>
     </row>
-    <row r="27" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>24</v>
       </c>
@@ -17789,7 +19666,7 @@
       <c r="BL27" s="2"/>
       <c r="BM27" s="2"/>
     </row>
-    <row r="28" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>25</v>
       </c>
@@ -17855,7 +19732,7 @@
       <c r="BL28" s="2"/>
       <c r="BM28" s="2"/>
     </row>
-    <row r="29" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>26</v>
       </c>
@@ -17921,7 +19798,7 @@
       <c r="BL29" s="2"/>
       <c r="BM29" s="2"/>
     </row>
-    <row r="30" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>34</v>
       </c>
@@ -17987,7 +19864,7 @@
       <c r="BL30" s="2"/>
       <c r="BM30" s="2"/>
     </row>
-    <row r="31" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>27</v>
       </c>
@@ -18053,7 +19930,7 @@
       <c r="BL31" s="2"/>
       <c r="BM31" s="2"/>
     </row>
-    <row r="32" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>28</v>
       </c>
@@ -18119,7 +19996,7 @@
       <c r="BL32" s="2"/>
       <c r="BM32" s="2"/>
     </row>
-    <row r="33" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>29</v>
       </c>
@@ -18185,7 +20062,7 @@
       <c r="BL33" s="2"/>
       <c r="BM33" s="2"/>
     </row>
-    <row r="34" spans="1:65" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>30</v>
       </c>
@@ -19597,12 +21474,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43736BA0-66D7-42CF-AF4E-9B35A47236D6}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.08984375" customWidth="1"/>
+    <col min="1" max="1" width="44.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>58</v>
       </c>
@@ -19732,35 +21609,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D754DB4-68D1-4883-8157-021E4015C684}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="14.90625" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.6328125" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" customWidth="1"/>
-    <col min="9" max="9" width="14.6328125" customWidth="1"/>
-    <col min="10" max="10" width="16.7265625" customWidth="1"/>
-    <col min="11" max="11" width="16.36328125" customWidth="1"/>
-    <col min="12" max="12" width="14.08984375" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" customWidth="1"/>
-    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="26"/>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
     </row>
-    <row r="5" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="24"/>
       <c r="B5" s="23" t="s">
         <v>56</v>
@@ -19783,7 +21660,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -19798,7 +21675,7 @@
       <c r="H6" s="20"/>
       <c r="I6" s="19"/>
     </row>
-    <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -19829,7 +21706,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -19860,7 +21737,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -19891,7 +21768,7 @@
         <v>-2.29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -19920,6 +21797,1193 @@
       <c r="J10" s="1">
         <f>SUM(E10:I10)</f>
         <v>4.0100000000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6990C3-08C9-429E-8881-6E83131F824F}">
+  <dimension ref="A1:AG43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="29">
+        <v>2015</v>
+      </c>
+      <c r="C3" s="29">
+        <v>2016</v>
+      </c>
+      <c r="D3" s="29">
+        <v>2017</v>
+      </c>
+      <c r="E3" s="29">
+        <v>2018</v>
+      </c>
+      <c r="F3" s="29">
+        <v>2019</v>
+      </c>
+      <c r="G3" s="29">
+        <v>2020</v>
+      </c>
+      <c r="H3" s="29">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="29">
+        <v>8.9</v>
+      </c>
+      <c r="C5" s="29">
+        <v>3.1</v>
+      </c>
+      <c r="D5" s="29">
+        <v>2.9</v>
+      </c>
+      <c r="E5" s="29">
+        <v>1.6</v>
+      </c>
+      <c r="F5" s="29">
+        <v>4</v>
+      </c>
+      <c r="G5" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="H5" s="29">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="K5" s="32">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L5" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="32">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="N5" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="O5" s="32">
+        <v>0.03</v>
+      </c>
+      <c r="P5" s="32">
+        <v>2.2000000000000002E-2</v>
+      </c>
+      <c r="Q5" s="32">
+        <v>0.11900000000000001</v>
+      </c>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="29">
+        <v>28.5</v>
+      </c>
+      <c r="C6" s="29">
+        <v>22.4</v>
+      </c>
+      <c r="D6" s="29">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E6" s="29">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F6" s="29">
+        <v>15.6</v>
+      </c>
+      <c r="G6" s="29">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="H6" s="29">
+        <v>16.8</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="K6" s="32">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="L6" s="32">
+        <v>0.22</v>
+      </c>
+      <c r="M6" s="32">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="N6" s="32">
+        <v>0.107</v>
+      </c>
+      <c r="O6" s="32">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="P6" s="32">
+        <v>0.22899999999999998</v>
+      </c>
+      <c r="Q6" s="32">
+        <v>0.312</v>
+      </c>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="29">
+        <v>38.9</v>
+      </c>
+      <c r="C7" s="29">
+        <v>47.2</v>
+      </c>
+      <c r="D7" s="29">
+        <v>38.9</v>
+      </c>
+      <c r="E7" s="29">
+        <v>42.4</v>
+      </c>
+      <c r="F7" s="29">
+        <v>45.9</v>
+      </c>
+      <c r="G7" s="29">
+        <v>54</v>
+      </c>
+      <c r="H7" s="29">
+        <v>35.5</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="K7" s="32">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="L7" s="32">
+        <v>0.217</v>
+      </c>
+      <c r="M7" s="32">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="N7" s="32">
+        <v>0.54299999999999993</v>
+      </c>
+      <c r="O7" s="32">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P7" s="32">
+        <v>0.501</v>
+      </c>
+      <c r="Q7" s="32">
+        <v>0.439</v>
+      </c>
+      <c r="S7" s="32"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="32"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="32"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="29">
+        <v>23.8</v>
+      </c>
+      <c r="C8" s="29">
+        <v>27.3</v>
+      </c>
+      <c r="D8" s="29">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="E8" s="29">
+        <v>39.1</v>
+      </c>
+      <c r="F8" s="29">
+        <v>34.5</v>
+      </c>
+      <c r="G8" s="29">
+        <v>25.7</v>
+      </c>
+      <c r="H8" s="29">
+        <v>42.8</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="K8" s="32">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="L8" s="32">
+        <v>0.38299999999999995</v>
+      </c>
+      <c r="M8" s="32">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="N8" s="32">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="O8" s="32">
+        <v>2.7000000000000003E-2</v>
+      </c>
+      <c r="P8" s="32">
+        <v>0.248</v>
+      </c>
+      <c r="Q8" s="32">
+        <v>0.129</v>
+      </c>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="32"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="29">
+        <v>15.7</v>
+      </c>
+      <c r="C10" s="29">
+        <v>14.6</v>
+      </c>
+      <c r="D10" s="29">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E10" s="29">
+        <v>6.9</v>
+      </c>
+      <c r="F10" s="29">
+        <v>12.2</v>
+      </c>
+      <c r="G10" s="29">
+        <v>7.1</v>
+      </c>
+      <c r="H10" s="29">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="29">
+        <v>25.9</v>
+      </c>
+      <c r="C11" s="29">
+        <v>24.6</v>
+      </c>
+      <c r="D11" s="29">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="29">
+        <v>27.4</v>
+      </c>
+      <c r="F11" s="29">
+        <v>20.7</v>
+      </c>
+      <c r="G11" s="29">
+        <v>23.3</v>
+      </c>
+      <c r="H11" s="29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="29">
+        <v>17.3</v>
+      </c>
+      <c r="C12" s="29">
+        <v>24.8</v>
+      </c>
+      <c r="D12" s="29">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E12" s="29">
+        <v>23.6</v>
+      </c>
+      <c r="F12" s="29">
+        <v>27.2</v>
+      </c>
+      <c r="G12" s="29">
+        <v>33.6</v>
+      </c>
+      <c r="H12" s="29">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="29">
+        <v>41.1</v>
+      </c>
+      <c r="C13" s="29">
+        <v>36.1</v>
+      </c>
+      <c r="D13" s="29">
+        <v>43.2</v>
+      </c>
+      <c r="E13" s="29">
+        <v>42.2</v>
+      </c>
+      <c r="F13" s="29">
+        <v>39.9</v>
+      </c>
+      <c r="G13" s="29">
+        <v>36</v>
+      </c>
+      <c r="H13" s="29">
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="29">
+        <v>19</v>
+      </c>
+      <c r="C15" s="29">
+        <v>13.7</v>
+      </c>
+      <c r="D15" s="29">
+        <v>20.7</v>
+      </c>
+      <c r="E15" s="29">
+        <v>5.9</v>
+      </c>
+      <c r="F15" s="29">
+        <v>13.8</v>
+      </c>
+      <c r="G15" s="29">
+        <v>7.4</v>
+      </c>
+      <c r="H15" s="29">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="29">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="C16" s="29">
+        <v>32.4</v>
+      </c>
+      <c r="D16" s="29">
+        <v>34.9</v>
+      </c>
+      <c r="E16" s="29">
+        <v>29.8</v>
+      </c>
+      <c r="F16" s="29">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="G16" s="29">
+        <v>45.3</v>
+      </c>
+      <c r="H16" s="29">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="29">
+        <v>36.4</v>
+      </c>
+      <c r="C17" s="29">
+        <v>40.1</v>
+      </c>
+      <c r="D17" s="29">
+        <v>33.6</v>
+      </c>
+      <c r="E17" s="29">
+        <v>50.9</v>
+      </c>
+      <c r="F17" s="29">
+        <v>41.9</v>
+      </c>
+      <c r="G17" s="29">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="H17" s="29">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="29">
+        <v>7.3</v>
+      </c>
+      <c r="C18" s="29">
+        <v>13.8</v>
+      </c>
+      <c r="D18" s="29">
+        <v>10.7</v>
+      </c>
+      <c r="E18" s="29">
+        <v>13.5</v>
+      </c>
+      <c r="F18" s="29">
+        <v>11.9</v>
+      </c>
+      <c r="G18" s="29">
+        <v>12.4</v>
+      </c>
+      <c r="H18" s="29">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="29">
+        <v>0</v>
+      </c>
+      <c r="C20" s="29">
+        <v>0</v>
+      </c>
+      <c r="D20" s="29">
+        <v>0</v>
+      </c>
+      <c r="E20" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="29">
+        <v>0</v>
+      </c>
+      <c r="G20" s="29">
+        <v>0</v>
+      </c>
+      <c r="H20" s="29">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="29">
+        <v>5.9</v>
+      </c>
+      <c r="C21" s="29">
+        <v>2.4</v>
+      </c>
+      <c r="D21" s="29">
+        <v>4.7</v>
+      </c>
+      <c r="E21" s="29">
+        <v>3.4</v>
+      </c>
+      <c r="F21" s="29">
+        <v>3.1</v>
+      </c>
+      <c r="G21" s="29">
+        <v>1.3</v>
+      </c>
+      <c r="H21" s="29">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="29">
+        <v>41.5</v>
+      </c>
+      <c r="C22" s="29">
+        <v>41.5</v>
+      </c>
+      <c r="D22" s="29">
+        <v>43.3</v>
+      </c>
+      <c r="E22" s="29">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F22" s="29">
+        <v>52.9</v>
+      </c>
+      <c r="G22" s="29">
+        <v>42.9</v>
+      </c>
+      <c r="H22" s="29">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="29">
+        <v>52.6</v>
+      </c>
+      <c r="C23" s="29">
+        <v>56.1</v>
+      </c>
+      <c r="D23" s="29">
+        <v>52.1</v>
+      </c>
+      <c r="E23" s="29">
+        <v>61.8</v>
+      </c>
+      <c r="F23" s="29">
+        <v>44.2</v>
+      </c>
+      <c r="G23" s="29">
+        <v>55.8</v>
+      </c>
+      <c r="H23" s="29">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="29">
+        <v>5.9</v>
+      </c>
+      <c r="C25" s="29">
+        <v>1.9</v>
+      </c>
+      <c r="D25" s="29">
+        <v>6.2</v>
+      </c>
+      <c r="E25" s="29">
+        <v>1.6</v>
+      </c>
+      <c r="F25" s="29">
+        <v>2.7</v>
+      </c>
+      <c r="G25" s="29">
+        <v>0</v>
+      </c>
+      <c r="H25" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="29">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="C26" s="29">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D26" s="29">
+        <v>24.7</v>
+      </c>
+      <c r="E26" s="29">
+        <v>12.8</v>
+      </c>
+      <c r="F26" s="29">
+        <v>23.8</v>
+      </c>
+      <c r="G26" s="29">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H26" s="29">
+        <v>36.299999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="29">
+        <v>38.1</v>
+      </c>
+      <c r="C27" s="29">
+        <v>44.7</v>
+      </c>
+      <c r="D27" s="29">
+        <v>37.4</v>
+      </c>
+      <c r="E27" s="29">
+        <v>43.5</v>
+      </c>
+      <c r="F27" s="29">
+        <v>45.3</v>
+      </c>
+      <c r="G27" s="29">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="H27" s="29">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="29">
+        <v>15.3</v>
+      </c>
+      <c r="C28" s="29">
+        <v>36.9</v>
+      </c>
+      <c r="D28" s="29">
+        <v>31.7</v>
+      </c>
+      <c r="E28" s="29">
+        <v>42.2</v>
+      </c>
+      <c r="F28" s="29">
+        <v>28.2</v>
+      </c>
+      <c r="G28" s="29">
+        <v>19.7</v>
+      </c>
+      <c r="H28" s="29">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="29">
+        <v>4.7</v>
+      </c>
+      <c r="C30" s="29">
+        <v>1.2</v>
+      </c>
+      <c r="D30" s="29">
+        <v>1.3</v>
+      </c>
+      <c r="E30" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="F30" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="G30" s="29">
+        <v>0.6</v>
+      </c>
+      <c r="H30" s="29">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="29">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="C31" s="29">
+        <v>15.3</v>
+      </c>
+      <c r="D31" s="29">
+        <v>25.4</v>
+      </c>
+      <c r="E31" s="29">
+        <v>7.8</v>
+      </c>
+      <c r="F31" s="29">
+        <v>7.6</v>
+      </c>
+      <c r="G31" s="29">
+        <v>5.3</v>
+      </c>
+      <c r="H31" s="29">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="29">
+        <v>60.9</v>
+      </c>
+      <c r="C32" s="29">
+        <v>65.7</v>
+      </c>
+      <c r="D32" s="29">
+        <v>47.7</v>
+      </c>
+      <c r="E32" s="29">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="F32" s="29">
+        <v>83.2</v>
+      </c>
+      <c r="G32" s="29">
+        <v>66.5</v>
+      </c>
+      <c r="H32" s="29">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="29">
+        <v>14.9</v>
+      </c>
+      <c r="C33" s="29">
+        <v>17.8</v>
+      </c>
+      <c r="D33" s="29">
+        <v>25.6</v>
+      </c>
+      <c r="E33" s="29">
+        <v>26.6</v>
+      </c>
+      <c r="F33" s="29">
+        <v>7.7</v>
+      </c>
+      <c r="G33" s="29">
+        <v>27.5</v>
+      </c>
+      <c r="H33" s="29">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="29">
+        <v>12.6</v>
+      </c>
+      <c r="C35" s="29">
+        <v>6.1</v>
+      </c>
+      <c r="D35" s="29">
+        <v>6.6</v>
+      </c>
+      <c r="E35" s="29">
+        <v>5</v>
+      </c>
+      <c r="F35" s="29">
+        <v>8.1</v>
+      </c>
+      <c r="G35" s="29">
+        <v>3.7</v>
+      </c>
+      <c r="H35" s="29">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="29">
+        <v>26.7</v>
+      </c>
+      <c r="C36" s="29">
+        <v>22.1</v>
+      </c>
+      <c r="D36" s="29">
+        <v>25.7</v>
+      </c>
+      <c r="E36" s="29">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F36" s="29">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="G36" s="29">
+        <v>16.7</v>
+      </c>
+      <c r="H36" s="29">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="29">
+        <v>40.4</v>
+      </c>
+      <c r="C37" s="29">
+        <v>51.3</v>
+      </c>
+      <c r="D37" s="29">
+        <v>56.6</v>
+      </c>
+      <c r="E37" s="29">
+        <v>47.5</v>
+      </c>
+      <c r="F37" s="29">
+        <v>69.5</v>
+      </c>
+      <c r="G37" s="29">
+        <v>58</v>
+      </c>
+      <c r="H37" s="29">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="29">
+        <v>20.3</v>
+      </c>
+      <c r="C38" s="29">
+        <v>20.5</v>
+      </c>
+      <c r="D38" s="29">
+        <v>11.1</v>
+      </c>
+      <c r="E38" s="29">
+        <v>28.5</v>
+      </c>
+      <c r="F38" s="29">
+        <v>6.4</v>
+      </c>
+      <c r="G38" s="29">
+        <v>21.6</v>
+      </c>
+      <c r="H38" s="29">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="29">
+        <v>2</v>
+      </c>
+      <c r="F39" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="H39" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="L39" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="N39" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="O39" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="P39" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q39" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="R39" s="29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H40" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="J40" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K40" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="L40" s="29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H42" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="J42" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K42" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="L42" s="29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I43" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="J43" s="29" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
